--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
+        <v>7</v>
+      </c>
+      <c r="G16" s="14">
         <v>9</v>
       </c>
-      <c r="G16" s="14">
-        <v>12</v>
-      </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J16" s="14">
         <v>14</v>
       </c>
       <c r="K16" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.411764705882</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M16" s="15">
-        <v>-57.142857142857</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.516853932584</v>
+        <v>-86.915887850467</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
         <v>0</v>
       </c>
       <c r="F17" s="14">
+        <v>19</v>
+      </c>
+      <c r="G17" s="14">
         <v>17</v>
       </c>
-      <c r="G17" s="14">
-        <v>16</v>
-      </c>
       <c r="H17" s="15">
-        <v>6.25</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I17" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J17" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.523809523809</v>
+        <v>-8</v>
       </c>
       <c r="L17" s="15">
-        <v>-29.629629629629</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>-26.923076923076</v>
+        <v>-28.125</v>
       </c>
       <c r="N17" s="15">
-        <v>-68.333333333333</v>
+        <v>-67.605633802816</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>-28.571428571428</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="14">
         <v>9</v>
       </c>
       <c r="J18" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K18" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="L18" s="15">
         <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>-10</v>
+        <v>-25</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.024390243902</v>
+        <v>-90.217391304347</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>7</v>
+      </c>
+      <c r="D19" s="14">
         <v>6</v>
       </c>
-      <c r="D19" s="14">
-        <v>5</v>
-      </c>
       <c r="E19" s="15">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>9.523809523809</v>
+        <v>10</v>
       </c>
       <c r="I19" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J19" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K19" s="15">
-        <v>34.782608695652</v>
+        <v>27.586206896551</v>
       </c>
       <c r="L19" s="15">
-        <v>-40.384615384615</v>
+        <v>-35.087719298245</v>
       </c>
       <c r="M19" s="15">
-        <v>6.896551724137</v>
+        <v>8.823529411764</v>
       </c>
       <c r="N19" s="15">
-        <v>-34.042553191489</v>
+        <v>-33.928571428571</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,20 +1100,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>4</v>
@@ -1125,13 +1125,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M20" s="15">
         <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-75</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>7.692307692307</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F21" s="17">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G21" s="17">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H21" s="18">
         <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J21" s="17">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K21" s="18">
-        <v>6.849315068493</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.973451327433</v>
+        <v>-28</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.75</v>
+        <v>-19.642857142857</v>
       </c>
       <c r="N21" s="18">
-        <v>-74</v>
+        <v>-74.789915966386</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L22" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
+        <v>6</v>
+      </c>
+      <c r="G23" s="14">
         <v>7</v>
       </c>
-      <c r="G23" s="14">
-        <v>10</v>
-      </c>
       <c r="H23" s="15">
-        <v>-30</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K23" s="15">
-        <v>-36.363636363636</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-46.153846153846</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>75</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E24" s="15">
-        <v>-41.666666666666</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G24" s="14">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="H24" s="15">
-        <v>-36.029411764705</v>
+        <v>-45.695364238410</v>
       </c>
       <c r="I24" s="14">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="J24" s="14">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="K24" s="15">
-        <v>-30.409356725146</v>
+        <v>-37.788018433179</v>
       </c>
       <c r="L24" s="15">
-        <v>19</v>
+        <v>13.445378151260</v>
       </c>
       <c r="M24" s="15">
-        <v>11.214953271028</v>
+        <v>15.384615384615</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E25" s="15">
-        <v>-69.230769230769</v>
+        <v>-82.352941176470</v>
       </c>
       <c r="F25" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G25" s="14">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="H25" s="15">
-        <v>-45.652173913043</v>
+        <v>-57.547169811320</v>
       </c>
       <c r="I25" s="14">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J25" s="14">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="K25" s="15">
-        <v>-43.589743589743</v>
+        <v>-51.655629139072</v>
       </c>
       <c r="L25" s="15">
-        <v>50</v>
+        <v>28.070175438596</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
         <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-44.444444444444</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.375</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="I26" s="14">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J26" s="14">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="K26" s="15">
-        <v>-32</v>
+        <v>-27.118644067796</v>
       </c>
       <c r="L26" s="15">
-        <v>-20.930232558139</v>
+        <v>-14</v>
       </c>
       <c r="M26" s="15">
-        <v>-40.350877192982</v>
+        <v>-29.508196721311</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
@@ -1429,28 +1429,28 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>3</v>
       </c>
       <c r="J28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="15">
         <v>-25</v>

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -901,14 +901,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -920,13 +920,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
         <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-22.222222222222</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.315789473684</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="M16" s="15">
-        <v>-54.838709677419</v>
+        <v>-59.459459459459</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.915887850467</v>
+        <v>-87.704918032786</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>11.764705882352</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J17" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K17" s="15">
-        <v>-8</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="L17" s="15">
-        <v>-23.333333333333</v>
+        <v>-21.875</v>
       </c>
       <c r="M17" s="15">
-        <v>-28.125</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N17" s="15">
-        <v>-67.605633802816</v>
+        <v>-71.264367816091</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
         <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-16.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J18" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K18" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
         <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>-25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.217391304347</v>
+        <v>-89.380530973451</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
         <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>10</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I19" s="14">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J19" s="14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K19" s="15">
-        <v>27.586206896551</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L19" s="15">
-        <v>-35.087719298245</v>
+        <v>-27.868852459016</v>
       </c>
       <c r="M19" s="15">
-        <v>8.823529411764</v>
+        <v>12.820512820512</v>
       </c>
       <c r="N19" s="15">
-        <v>-33.928571428571</v>
+        <v>-27.868852459016</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="14">
         <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="15">
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M20" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.818181818181</v>
+        <v>-78.260869565217</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,60 +1142,60 @@
         <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>27.272727272727</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F21" s="17">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G21" s="17">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-21.875</v>
       </c>
       <c r="I21" s="17">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="J21" s="17">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="K21" s="18">
-        <v>7.142857142857</v>
+        <v>1.960784313725</v>
       </c>
       <c r="L21" s="18">
-        <v>-28</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.642857142857</v>
+        <v>-18.75</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.789915966386</v>
+        <v>-75.059952038369</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I22" s="14">
         <v>5</v>
@@ -1210,7 +1210,7 @@
         <v>-16.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-14.285714285714</v>
+        <v>-62.5</v>
       </c>
       <c r="I23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-33.333333333333</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L23" s="15">
-        <v>-46.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="M23" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>-65.217391304347</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F24" s="14">
         <v>82</v>
       </c>
       <c r="G24" s="14">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H24" s="15">
-        <v>-45.695364238410</v>
+        <v>-46.052631578947</v>
       </c>
       <c r="I24" s="14">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="J24" s="14">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="K24" s="15">
-        <v>-37.788018433179</v>
+        <v>-38</v>
       </c>
       <c r="L24" s="15">
-        <v>13.445378151260</v>
+        <v>13.970588235294</v>
       </c>
       <c r="M24" s="15">
-        <v>15.384615384615</v>
+        <v>23.015873015873</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15">
-        <v>-82.352941176470</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G25" s="14">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H25" s="15">
-        <v>-57.547169811320</v>
+        <v>-56.880733944954</v>
       </c>
       <c r="I25" s="14">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J25" s="14">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="K25" s="15">
-        <v>-51.655629139072</v>
+        <v>-50.857142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>28.070175438596</v>
+        <v>26.470588235294</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>-24.242424242424</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I26" s="14">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="J26" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K26" s="15">
-        <v>-27.118644067796</v>
+        <v>-17.1875</v>
       </c>
       <c r="L26" s="15">
-        <v>-14</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="M26" s="15">
-        <v>-29.508196721311</v>
+        <v>-19.696969696969</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,14 +1393,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>1</v>
@@ -1444,16 +1444,16 @@
         <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
         <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,31 +869,31 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,32 +901,32 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-100</v>
+      <c r="F15" s="14">
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="L15" s="15">
+        <v>150</v>
+      </c>
+      <c r="M15" s="15">
+        <v>400</v>
+      </c>
+      <c r="N15" s="15">
         <v>0</v>
-      </c>
-      <c r="L15" s="15">
-        <v>50</v>
-      </c>
-      <c r="M15" s="15">
-        <v>200</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F16" s="14">
         <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-45.454545454545</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>-11.764705882352</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.307692307692</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-59.459459459459</v>
+        <v>-56.410256410256</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.704918032786</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.666666666666</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I17" s="14">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J17" s="14">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.714285714285</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="L17" s="15">
-        <v>-21.875</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M17" s="15">
-        <v>-28.571428571428</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="N17" s="15">
-        <v>-71.264367816091</v>
+        <v>-65.957446808510</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
         <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I18" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J18" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K18" s="15">
         <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M18" s="15">
-        <v>-14.285714285714</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.380530973451</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F19" s="14">
+        <v>30</v>
+      </c>
+      <c r="G19" s="14">
         <v>22</v>
       </c>
-      <c r="G19" s="14">
-        <v>21</v>
-      </c>
       <c r="H19" s="15">
-        <v>4.761904761904</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I19" s="14">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J19" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K19" s="15">
-        <v>22.222222222222</v>
+        <v>40</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.868852459016</v>
+        <v>-25.333333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>12.820512820512</v>
+        <v>19.148936170212</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.868852459016</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,20 +1100,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>1</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
         <v>5</v>
@@ -1131,7 +1131,7 @@
         <v>150</v>
       </c>
       <c r="N20" s="15">
-        <v>-78.260869565217</v>
+        <v>-81.481481481481</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.222222222222</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G21" s="17">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.875</v>
+        <v>4.838709677419</v>
       </c>
       <c r="I21" s="17">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="J21" s="17">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="K21" s="18">
-        <v>1.960784313725</v>
+        <v>7.377049180327</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.272727272727</v>
+        <v>-25.142857142857</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.75</v>
+        <v>-11.486486486486</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.059952038369</v>
+        <v>-72.421052631578</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
         <v>5</v>
@@ -1210,7 +1210,7 @@
         <v>-16.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
         <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>-62.5</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J23" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>-35.714285714285</v>
+        <v>-12.5</v>
       </c>
       <c r="L23" s="15">
-        <v>-40</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M23" s="15">
-        <v>28.571428571428</v>
+        <v>55.555555555555</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>-36.363636363636</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="F24" s="14">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G24" s="14">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H24" s="15">
-        <v>-46.052631578947</v>
+        <v>-48.591549295774</v>
       </c>
       <c r="I24" s="14">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="J24" s="14">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="K24" s="15">
-        <v>-38</v>
+        <v>-38.628158844765</v>
       </c>
       <c r="L24" s="15">
-        <v>13.970588235294</v>
+        <v>5.590062111801</v>
       </c>
       <c r="M24" s="15">
-        <v>23.015873015873</v>
+        <v>25.925925925925</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-45.833333333333</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G25" s="14">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H25" s="15">
-        <v>-56.880733944954</v>
+        <v>-62.264150943396</v>
       </c>
       <c r="I25" s="14">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J25" s="14">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="K25" s="15">
-        <v>-50.857142857142</v>
+        <v>-50.253807106599</v>
       </c>
       <c r="L25" s="15">
-        <v>26.470588235294</v>
+        <v>19.512195121951</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.448275862068</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J26" s="14">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K26" s="15">
-        <v>-17.1875</v>
+        <v>-16.438356164383</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.114754098360</v>
+        <v>-6.153846153846</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.696969696969</v>
+        <v>-14.084507042253</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-100</v>
+      <c r="F27" s="14">
+        <v>2</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1434,26 +1434,26 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="14">
-        <v>1</v>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J28" s="14">
         <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>-20</v>
+        <v>-60</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,31 +1484,31 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,23 +1525,23 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-83.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-40</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I16" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K16" s="15">
-        <v>-26.086956521739</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>-43.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.410256410256</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.5</v>
+        <v>-86.754966887417</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,63 +975,63 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
+        <v>14</v>
+      </c>
+      <c r="G17" s="14">
         <v>17</v>
       </c>
-      <c r="G17" s="14">
-        <v>19</v>
-      </c>
       <c r="H17" s="15">
+        <v>-17.647058823529</v>
+      </c>
+      <c r="I17" s="14">
+        <v>34</v>
+      </c>
+      <c r="J17" s="14">
+        <v>38</v>
+      </c>
+      <c r="K17" s="15">
         <v>-10.526315789473</v>
       </c>
-      <c r="I17" s="14">
-        <v>32</v>
-      </c>
-      <c r="J17" s="14">
-        <v>35</v>
-      </c>
-      <c r="K17" s="15">
-        <v>-8.571428571428</v>
-      </c>
       <c r="L17" s="15">
-        <v>-15.789473684210</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M17" s="15">
-        <v>-21.951219512195</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="N17" s="15">
-        <v>-65.957446808510</v>
+        <v>-68.224299065420</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
-      </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
+        <v>7</v>
+      </c>
+      <c r="G18" s="14">
         <v>8</v>
       </c>
-      <c r="G18" s="14">
-        <v>9</v>
-      </c>
       <c r="H18" s="15">
-        <v>-11.111111111111</v>
+        <v>-12.5</v>
       </c>
       <c r="I18" s="14">
         <v>15</v>
@@ -1043,13 +1043,13 @@
         <v>0</v>
       </c>
       <c r="L18" s="15">
+        <v>-28.571428571428</v>
+      </c>
+      <c r="M18" s="15">
         <v>-21.052631578947</v>
       </c>
-      <c r="M18" s="15">
-        <v>-16.666666666666</v>
-      </c>
       <c r="N18" s="15">
-        <v>-88.888888888888</v>
+        <v>-90.131578947368</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>150</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H19" s="15">
-        <v>36.363636363636</v>
+        <v>34.782608695652</v>
       </c>
       <c r="I19" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J19" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K19" s="15">
-        <v>40</v>
+        <v>34.782608695652</v>
       </c>
       <c r="L19" s="15">
-        <v>-25.333333333333</v>
+        <v>-27.906976744186</v>
       </c>
       <c r="M19" s="15">
-        <v>19.148936170212</v>
+        <v>21.568627450980</v>
       </c>
       <c r="N19" s="15">
-        <v>-20</v>
+        <v>-18.421052631578</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
+        <v>2</v>
+      </c>
+      <c r="G20" s="14">
         <v>1</v>
       </c>
-      <c r="G20" s="14">
-        <v>2</v>
-      </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="14">
         <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>-44.444444444444</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.481481481481</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F21" s="17">
         <v>65</v>
       </c>
       <c r="G21" s="17">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H21" s="18">
-        <v>4.838709677419</v>
+        <v>3.174603174603</v>
       </c>
       <c r="I21" s="17">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J21" s="17">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="K21" s="18">
-        <v>7.377049180327</v>
+        <v>5.147058823529</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.142857142857</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.486486486486</v>
+        <v>-11.728395061728</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.421052631578</v>
+        <v>-73.170731707317</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>5</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>4</v>
-      </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>100</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>14.285714285714</v>
+        <v>60</v>
       </c>
       <c r="I23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="14">
         <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>-12.5</v>
+        <v>-6.25</v>
       </c>
       <c r="L23" s="15">
-        <v>-22.222222222222</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M23" s="15">
-        <v>55.555555555555</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-40.740740740740</v>
+        <v>40</v>
       </c>
       <c r="F24" s="14">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="H24" s="15">
-        <v>-48.591549295774</v>
+        <v>-36.507936507936</v>
       </c>
       <c r="I24" s="14">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="J24" s="14">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="K24" s="15">
-        <v>-38.628158844765</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L24" s="15">
-        <v>5.590062111801</v>
+        <v>10</v>
       </c>
       <c r="M24" s="15">
-        <v>25.925925925925</v>
+        <v>37.5</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-6.25</v>
       </c>
       <c r="F25" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G25" s="14">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H25" s="15">
-        <v>-62.264150943396</v>
+        <v>-52.083333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="J25" s="14">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="K25" s="15">
-        <v>-50.253807106599</v>
+        <v>-46.948356807511</v>
       </c>
       <c r="L25" s="15">
-        <v>19.512195121951</v>
+        <v>18.947368421052</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>39.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="J26" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K26" s="15">
-        <v>-16.438356164383</v>
+        <v>-6.410256410256</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.153846153846</v>
+        <v>1.388888888888</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.084507042253</v>
+        <v>-3.947368421052</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F28" s="14">
+        <v>1</v>
       </c>
       <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-75</v>
+      </c>
+      <c r="I28" s="14">
         <v>3</v>
       </c>
-      <c r="H28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I28" s="14">
-        <v>2</v>
-      </c>
       <c r="J28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>-60</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.736842105263</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -885,7 +885,7 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-87.5</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
+        <v>300</v>
+      </c>
+      <c r="F16" s="14">
+        <v>9</v>
+      </c>
+      <c r="G16" s="14">
+        <v>15</v>
+      </c>
+      <c r="H16" s="15">
         <v>-40</v>
       </c>
-      <c r="F16" s="14">
-        <v>8</v>
-      </c>
-      <c r="G16" s="14">
-        <v>14</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-42.857142857142</v>
-      </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K16" s="15">
-        <v>-28.571428571428</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.857142857142</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.521739130434</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.754966887417</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>9</v>
+      </c>
+      <c r="D17" s="14">
         <v>2</v>
       </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>350</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>-17.647058823529</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.526315789473</v>
+        <v>10</v>
       </c>
       <c r="L17" s="15">
-        <v>-19.047619047619</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="M17" s="15">
-        <v>-20.930232558139</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="N17" s="15">
-        <v>-68.224299065420</v>
+        <v>-62.393162393162</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K18" s="15">
         <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.052631578947</v>
+        <v>-10</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.131578947368</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>16.666666666666</v>
+        <v>233.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>34.782608695652</v>
+        <v>70</v>
       </c>
       <c r="I19" s="14">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="J19" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K19" s="15">
-        <v>34.782608695652</v>
+        <v>46.938775510204</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.906976744186</v>
+        <v>-28.712871287128</v>
       </c>
       <c r="M19" s="15">
-        <v>21.568627450980</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N19" s="15">
-        <v>-18.421052631578</v>
+        <v>-7.692307692307</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>3</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>-12.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-40</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.818181818181</v>
+        <v>-81.081081081081</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.142857142857</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G21" s="17">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>3.174603174603</v>
+        <v>20.3125</v>
       </c>
       <c r="I21" s="17">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="J21" s="17">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="K21" s="18">
-        <v>5.147058823529</v>
+        <v>15.540540540540</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.777777777777</v>
+        <v>-24</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.728395061728</v>
+        <v>-1.724137931034</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.170731707317</v>
+        <v>-70.918367346938</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1191,26 +1191,26 @@
       <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>3</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J23" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K23" s="15">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-21.052631578947</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M23" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>40</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="F24" s="14">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G24" s="14">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H24" s="15">
-        <v>-36.507936507936</v>
+        <v>-26.548672566371</v>
       </c>
       <c r="I24" s="14">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="J24" s="14">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="K24" s="15">
-        <v>-33.333333333333</v>
+        <v>-34.242424242424</v>
       </c>
       <c r="L24" s="15">
-        <v>10</v>
+        <v>7.960199004975</v>
       </c>
       <c r="M24" s="15">
-        <v>37.5</v>
+        <v>37.341772151898</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-6.25</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F25" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G25" s="14">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="H25" s="15">
-        <v>-52.083333333333</v>
+        <v>-39.240506329113</v>
       </c>
       <c r="I25" s="14">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="J25" s="14">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="K25" s="15">
-        <v>-46.948356807511</v>
+        <v>-47.391304347826</v>
       </c>
       <c r="L25" s="15">
-        <v>18.947368421052</v>
+        <v>10</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>39.285714285714</v>
+        <v>63.636363636363</v>
       </c>
       <c r="I26" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J26" s="14">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.410256410256</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="L26" s="15">
-        <v>1.388888888888</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
-        <v>-3.947368421052</v>
+        <v>-8.235294117647</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I28" s="14">
+        <v>4</v>
+      </c>
+      <c r="J28" s="14">
+        <v>8</v>
+      </c>
+      <c r="K28" s="15">
         <v>-50</v>
       </c>
-      <c r="F28" s="14">
-        <v>1</v>
-      </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-75</v>
-      </c>
-      <c r="I28" s="14">
-        <v>3</v>
-      </c>
-      <c r="J28" s="14">
-        <v>7</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-57.142857142857</v>
-      </c>
       <c r="L28" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="M29" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-95</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.444444444444</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-40</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J16" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K16" s="15">
-        <v>-17.241379310344</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.135135135135</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-46</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.714285714285</v>
+        <v>-84.916201117318</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>26.666666666666</v>
+        <v>47.058823529411</v>
       </c>
       <c r="I17" s="14">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J17" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K17" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.382978723404</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="M17" s="15">
-        <v>-6.382978723404</v>
+        <v>10.204081632653</v>
       </c>
       <c r="N17" s="15">
-        <v>-62.393162393162</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="14">
         <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L18" s="15">
         <v>-25</v>
       </c>
       <c r="M18" s="15">
-        <v>-10</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.473684210526</v>
+        <v>-90.526315789473</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,63 +1057,63 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>233.333333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H19" s="15">
-        <v>70</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I19" s="14">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J19" s="14">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="K19" s="15">
-        <v>46.938775510204</v>
+        <v>32.758620689655</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.712871287128</v>
+        <v>-32.456140350877</v>
       </c>
       <c r="M19" s="15">
-        <v>28.571428571428</v>
+        <v>24.193548387096</v>
       </c>
       <c r="N19" s="15">
-        <v>-7.692307692307</v>
+        <v>-7.228915662650</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-33.333333333333</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>7</v>
@@ -1125,13 +1125,13 @@
         <v>-12.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-41.666666666666</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M20" s="15">
         <v>250</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.081081081081</v>
+        <v>-82.926829268292</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>133.333333333333</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
         <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>20.3125</v>
+        <v>17.1875</v>
       </c>
       <c r="I21" s="17">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="J21" s="17">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="K21" s="18">
-        <v>15.540540540540</v>
+        <v>13.855421686747</v>
       </c>
       <c r="L21" s="18">
-        <v>-24</v>
+        <v>-25.296442687747</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.724137931034</v>
+        <v>1.069518716577</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.918367346938</v>
+        <v>-70.283018867924</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>3</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>200</v>
       </c>
       <c r="F22" s="14">
+        <v>4</v>
+      </c>
+      <c r="G22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="H22" s="15">
+        <v>300</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="15">
         <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="I23" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K23" s="15">
+        <v>15.789473684210</v>
+      </c>
+      <c r="L23" s="15">
         <v>0</v>
       </c>
-      <c r="L23" s="15">
-        <v>-14.285714285714</v>
-      </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>144.444444444444</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>-42.424242424242</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G24" s="14">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.548672566371</v>
+        <v>-20.909090909090</v>
       </c>
       <c r="I24" s="14">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="J24" s="14">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="K24" s="15">
-        <v>-34.242424242424</v>
+        <v>-33.055555555555</v>
       </c>
       <c r="L24" s="15">
-        <v>7.960199004975</v>
+        <v>6.637168141592</v>
       </c>
       <c r="M24" s="15">
-        <v>37.341772151898</v>
+        <v>35.393258426966</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-58.823529411764</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="F25" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G25" s="14">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H25" s="15">
-        <v>-39.240506329113</v>
+        <v>-31.081081081081</v>
       </c>
       <c r="I25" s="14">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="J25" s="14">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="K25" s="15">
-        <v>-47.391304347826</v>
+        <v>-44.578313253012</v>
       </c>
       <c r="L25" s="15">
-        <v>10</v>
+        <v>9.523809523809</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H26" s="15">
-        <v>63.636363636363</v>
+        <v>24</v>
       </c>
       <c r="I26" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J26" s="14">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.703703703703</v>
+        <v>-7.865168539325</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>-3.529411764705</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.235294117647</v>
+        <v>-15.463917525773</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L28" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>-75</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="15">
         <v>-96</v>
@@ -1538,7 +1538,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
         <v>-95.238095238095</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -885,7 +885,7 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -920,10 +920,10 @@
         <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="M15" s="15">
         <v>150</v>
-      </c>
-      <c r="M15" s="15">
-        <v>400</v>
       </c>
       <c r="N15" s="15">
         <v>-16.666666666666</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-21.428571428571</v>
+        <v>10</v>
       </c>
       <c r="I16" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J16" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K16" s="15">
-        <v>-12.903225806451</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.714285714285</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-46</v>
+        <v>-45.098039215686</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.916201117318</v>
+        <v>-85.929648241206</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
         <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>80</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="14">
         <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>47.058823529411</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J17" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K17" s="15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L17" s="15">
-        <v>-3.571428571428</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>10.204081632653</v>
+        <v>13.725490196078</v>
       </c>
       <c r="N17" s="15">
-        <v>-57.142857142857</v>
+        <v>-56.716417910447</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-25</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>-10</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="L18" s="15">
-        <v>-25</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.739130434782</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.526315789473</v>
+        <v>-91.037735849056</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>36.363636363636</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I19" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J19" s="14">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K19" s="15">
-        <v>32.758620689655</v>
+        <v>20.588235294117</v>
       </c>
       <c r="L19" s="15">
-        <v>-32.456140350877</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>24.193548387096</v>
+        <v>17.142857142857</v>
       </c>
       <c r="N19" s="15">
-        <v>-7.228915662650</v>
+        <v>-14.583333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1125,13 +1125,13 @@
         <v>-12.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-46.153846153846</v>
+        <v>-50</v>
       </c>
       <c r="M20" s="15">
         <v>250</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.926829268292</v>
+        <v>-83.720930232558</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.555555555555</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H21" s="18">
-        <v>17.1875</v>
+        <v>7.936507936507</v>
       </c>
       <c r="I21" s="17">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="J21" s="17">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="K21" s="18">
-        <v>13.855421686747</v>
+        <v>8.108108108108</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.296442687747</v>
+        <v>-25.373134328358</v>
       </c>
       <c r="M21" s="18">
-        <v>1.069518716577</v>
+        <v>0</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.283018867924</v>
+        <v>-71.509971509971</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>3</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>200</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
@@ -1210,7 +1210,7 @@
         <v>28.571428571428</v>
       </c>
       <c r="M22" s="15">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
-      </c>
-      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="15">
-        <v>300</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>120</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I23" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J23" s="14">
         <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>15.789473684210</v>
+        <v>21.052631578947</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="M23" s="15">
-        <v>144.444444444444</v>
+        <v>155.555555555556</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.333333333333</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G24" s="14">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.909090909090</v>
+        <v>-14.035087719298</v>
       </c>
       <c r="I24" s="14">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="J24" s="14">
-        <v>360</v>
+        <v>391</v>
       </c>
       <c r="K24" s="15">
-        <v>-33.055555555555</v>
+        <v>-31.457800511509</v>
       </c>
       <c r="L24" s="15">
-        <v>6.637168141592</v>
+        <v>8.064516129032</v>
       </c>
       <c r="M24" s="15">
-        <v>35.393258426966</v>
+        <v>29.468599033816</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-10.526315789473</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G25" s="14">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H25" s="15">
-        <v>-31.081081081081</v>
+        <v>-16.417910447761</v>
       </c>
       <c r="I25" s="14">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="J25" s="14">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="K25" s="15">
-        <v>-44.578313253012</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>9.523809523809</v>
+        <v>6.944444444444</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H26" s="15">
-        <v>24</v>
+        <v>18.518518518518</v>
       </c>
       <c r="I26" s="14">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J26" s="14">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.865168539325</v>
+        <v>-8</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.529411764705</v>
+        <v>-2.127659574468</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.463917525773</v>
+        <v>-10.679611650485</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,8 +1393,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-96</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.238095238095</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,22 +870,22 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
+        <v>100</v>
+      </c>
+      <c r="L14" s="15">
         <v>0</v>
       </c>
-      <c r="L14" s="15">
-        <v>-50</v>
-      </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-91.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
         <v>66.666666666666</v>
@@ -926,7 +926,7 @@
         <v>150</v>
       </c>
       <c r="N15" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
         <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>10</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J16" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.151515151515</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-38</v>
       </c>
       <c r="M16" s="15">
-        <v>-45.098039215686</v>
+        <v>-41.509433962264</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.929648241206</v>
+        <v>-85.648148148148</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-40</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H17" s="15">
-        <v>66.666666666666</v>
+        <v>38.095238095238</v>
       </c>
       <c r="I17" s="14">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J17" s="14">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="K17" s="15">
-        <v>16</v>
+        <v>15.254237288135</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>4.615384615384</v>
       </c>
       <c r="M17" s="15">
-        <v>13.725490196078</v>
+        <v>25.925925925925</v>
       </c>
       <c r="N17" s="15">
-        <v>-56.716417910447</v>
+        <v>-54.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>-12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>-13.636363636363</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L18" s="15">
-        <v>-26.923076923076</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M18" s="15">
-        <v>-20.833333333333</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.037735849056</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.142857142857</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="I19" s="14">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J19" s="14">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K19" s="15">
-        <v>20.588235294117</v>
+        <v>16</v>
       </c>
       <c r="L19" s="15">
-        <v>-33.333333333333</v>
+        <v>-32.558139534883</v>
       </c>
       <c r="M19" s="15">
-        <v>17.142857142857</v>
+        <v>14.473684210526</v>
       </c>
       <c r="N19" s="15">
-        <v>-14.583333333333</v>
+        <v>-13.861386138613</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,29 +1100,29 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
         <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L20" s="15">
         <v>-50</v>
@@ -1131,7 +1131,7 @@
         <v>250</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.720930232558</v>
+        <v>-84.782608695652</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-47.368421052631</v>
+        <v>-15</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>7.936507936507</v>
+        <v>8.695652173913</v>
       </c>
       <c r="I21" s="17">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="J21" s="17">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="K21" s="18">
-        <v>8.108108108108</v>
+        <v>8.292682926829</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.373134328358</v>
+        <v>-23.972602739726</v>
       </c>
       <c r="M21" s="18">
-        <v>0</v>
+        <v>3.738317757009</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.509971509971</v>
+        <v>-70.904325032765</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>100</v>
       </c>
       <c r="F22" s="14">
+        <v>6</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>200</v>
+      </c>
+      <c r="I22" s="14">
+        <v>11</v>
+      </c>
+      <c r="J22" s="14">
         <v>4</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>300</v>
-      </c>
-      <c r="I22" s="14">
-        <v>9</v>
-      </c>
-      <c r="J22" s="14">
-        <v>3</v>
-      </c>
       <c r="K22" s="15">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="L22" s="15">
-        <v>28.571428571428</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M22" s="15">
-        <v>80</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>166.666666666667</v>
+        <v>140</v>
       </c>
       <c r="I23" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J23" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K23" s="15">
-        <v>21.052631578947</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.538461538461</v>
+        <v>3.703703703703</v>
       </c>
       <c r="M23" s="15">
-        <v>155.555555555556</v>
+        <v>211.111111111111</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>26</v>
+      </c>
+      <c r="D24" s="14">
         <v>27</v>
       </c>
-      <c r="D24" s="14">
-        <v>31</v>
-      </c>
       <c r="E24" s="15">
-        <v>-12.903225806451</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="F24" s="14">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G24" s="14">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.035087719298</v>
+        <v>-21.487603305785</v>
       </c>
       <c r="I24" s="14">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="J24" s="14">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="K24" s="15">
-        <v>-31.457800511509</v>
+        <v>-29.904306220095</v>
       </c>
       <c r="L24" s="15">
-        <v>8.064516129032</v>
+        <v>3.169014084507</v>
       </c>
       <c r="M24" s="15">
-        <v>29.468599033816</v>
+        <v>30.803571428571</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>6.666666666666</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F25" s="14">
         <v>56</v>
       </c>
       <c r="G25" s="14">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H25" s="15">
-        <v>-16.417910447761</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="14">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="J25" s="14">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="K25" s="15">
-        <v>-41.666666666666</v>
+        <v>-39.929328621908</v>
       </c>
       <c r="L25" s="15">
-        <v>6.944444444444</v>
+        <v>0</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>-9.090909090909</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>18.518518518518</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J26" s="14">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="K26" s="15">
-        <v>-8</v>
+        <v>-17.699115044247</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.127659574468</v>
+        <v>-3.125</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.679611650485</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
         <v>20</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
+        <v>2</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>5</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="15">
-        <v>-54.545454545454</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.153846153846</v>
+        <v>-92.592592592592</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.454545454545</v>
+        <v>-91.304347826087</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -926,30 +926,30 @@
         <v>150</v>
       </c>
       <c r="N15" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>200</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>83.333333333333</v>
+        <v>40</v>
       </c>
       <c r="I16" s="14">
         <v>31</v>
@@ -961,13 +961,13 @@
         <v>-8.823529411764</v>
       </c>
       <c r="L16" s="15">
-        <v>-38</v>
+        <v>-45.614035087719</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.509433962264</v>
+        <v>-46.551724137931</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.648148148148</v>
+        <v>-86.343612334801</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>38.095238095238</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I17" s="14">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J17" s="14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K17" s="15">
-        <v>15.254237288135</v>
+        <v>12.903225806451</v>
       </c>
       <c r="L17" s="15">
-        <v>4.615384615384</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="M17" s="15">
-        <v>25.925925925925</v>
+        <v>25</v>
       </c>
       <c r="N17" s="15">
-        <v>-54.666666666666</v>
+        <v>-56.790123456790</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>-12.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
         <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>-4.347826086956</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L18" s="15">
+        <v>-26.666666666666</v>
+      </c>
+      <c r="M18" s="15">
         <v>-24.137931034482</v>
       </c>
-      <c r="M18" s="15">
-        <v>-18.518518518518</v>
-      </c>
       <c r="N18" s="15">
-        <v>-90.476190476190</v>
+        <v>-91.020408163265</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
         <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-28.571428571428</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.793103448275</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="I19" s="14">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J19" s="14">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K19" s="15">
-        <v>16</v>
+        <v>10.975609756097</v>
       </c>
       <c r="L19" s="15">
-        <v>-32.558139534883</v>
+        <v>-34.532374100719</v>
       </c>
       <c r="M19" s="15">
-        <v>14.473684210526</v>
+        <v>13.75</v>
       </c>
       <c r="N19" s="15">
-        <v>-13.861386138613</v>
+        <v>-23.529411764705</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14">
         <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L20" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.782608695652</v>
+        <v>-82.978723404255</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>-15</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>8.695652173913</v>
+        <v>-22.058823529411</v>
       </c>
       <c r="I21" s="17">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="J21" s="17">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="K21" s="18">
-        <v>8.292682926829</v>
+        <v>6.018518518518</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.972602739726</v>
+        <v>-27.760252365930</v>
       </c>
       <c r="M21" s="18">
-        <v>3.738317757009</v>
+        <v>0</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.904325032765</v>
+        <v>-72.073170731707</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>100</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I22" s="14">
         <v>11</v>
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="14">
+        <v>9</v>
+      </c>
+      <c r="G23" s="14">
         <v>4</v>
       </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>100</v>
-      </c>
-      <c r="F23" s="14">
-        <v>12</v>
-      </c>
-      <c r="G23" s="14">
-        <v>5</v>
-      </c>
       <c r="H23" s="15">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="I23" s="14">
         <v>28</v>
       </c>
       <c r="J23" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K23" s="15">
-        <v>33.333333333333</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L23" s="15">
         <v>3.703703703703</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.703703703703</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F24" s="14">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G24" s="14">
         <v>121</v>
       </c>
       <c r="H24" s="15">
-        <v>-21.487603305785</v>
+        <v>-16.528925619834</v>
       </c>
       <c r="I24" s="14">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="J24" s="14">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="K24" s="15">
-        <v>-29.904306220095</v>
+        <v>-29.711751662971</v>
       </c>
       <c r="L24" s="15">
-        <v>3.169014084507</v>
+        <v>3.257328990228</v>
       </c>
       <c r="M24" s="15">
-        <v>30.803571428571</v>
+        <v>31.535269709543</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15">
-        <v>-15.789473684210</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G25" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H25" s="15">
-        <v>-20</v>
+        <v>-19.480519480519</v>
       </c>
       <c r="I25" s="14">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="J25" s="14">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="K25" s="15">
-        <v>-39.929328621908</v>
+        <v>-40.390879478827</v>
       </c>
       <c r="L25" s="15">
-        <v>0</v>
+        <v>-3.684210526315</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-69.230769230769</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H26" s="15">
-        <v>-34.285714285714</v>
+        <v>-40</v>
       </c>
       <c r="I26" s="14">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J26" s="14">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="K26" s="15">
-        <v>-17.699115044247</v>
+        <v>-17.355371900826</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.125</v>
+        <v>-2.912621359223</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.216216216216</v>
+        <v>-18.032786885245</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>3</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
         <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="L28" s="15">
-        <v>-61.538461538461</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M29" s="15">
         <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.592592592592</v>
+        <v>-93.103448275862</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
         <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.304347826087</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,73 +901,73 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>40</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J16" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.823529411764</v>
+        <v>-13.513513513513</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.614035087719</v>
+        <v>-47.540983606557</v>
       </c>
       <c r="M16" s="15">
-        <v>-46.551724137931</v>
+        <v>-47.540983606557</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.343612334801</v>
+        <v>-86.610878661087</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>37.5</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
-        <v>-4.545454545454</v>
+        <v>-12</v>
       </c>
       <c r="I17" s="14">
+        <v>81</v>
+      </c>
+      <c r="J17" s="14">
         <v>70</v>
       </c>
-      <c r="J17" s="14">
-        <v>62</v>
-      </c>
       <c r="K17" s="15">
-        <v>12.903225806451</v>
+        <v>15.714285714285</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.777777777777</v>
+        <v>1.25</v>
       </c>
       <c r="M17" s="15">
-        <v>25</v>
+        <v>37.288135593220</v>
       </c>
       <c r="N17" s="15">
-        <v>-56.790123456790</v>
+        <v>-53.977272727272</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K18" s="15">
-        <v>-8.333333333333</v>
+        <v>-4</v>
       </c>
       <c r="L18" s="15">
-        <v>-26.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="M18" s="15">
-        <v>-24.137931034482</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.020408163265</v>
+        <v>-90.697674418604</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,72 +1057,72 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
         <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="14">
         <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>-42.424242424242</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="I19" s="14">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J19" s="14">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K19" s="15">
-        <v>10.975609756097</v>
+        <v>7.865168539325</v>
       </c>
       <c r="L19" s="15">
-        <v>-34.532374100719</v>
+        <v>-36.423841059602</v>
       </c>
       <c r="M19" s="15">
-        <v>13.75</v>
+        <v>11.627906976744</v>
       </c>
       <c r="N19" s="15">
-        <v>-23.529411764705</v>
+        <v>-26.717557251908</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>1</v>
       </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" s="15">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="L20" s="15">
         <v>-42.857142857142</v>
@@ -1131,7 +1131,7 @@
         <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.978723404255</v>
+        <v>-84.313725490196</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.363636363636</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.058823529411</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="J21" s="17">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="K21" s="18">
-        <v>6.018518518518</v>
+        <v>5.508474576271</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.760252365930</v>
+        <v>-26.979472140762</v>
       </c>
       <c r="M21" s="18">
-        <v>0</v>
+        <v>1.632653061224</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.073170731707</v>
+        <v>-71.542857142857</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="L22" s="15">
-        <v>57.142857142857</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M22" s="15">
-        <v>83.333333333333</v>
+        <v>116.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="C23" s="14">
+        <v>3</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>125</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I23" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J23" s="14">
         <v>22</v>
       </c>
       <c r="K23" s="15">
-        <v>27.272727272727</v>
+        <v>40.909090909090</v>
       </c>
       <c r="L23" s="15">
-        <v>3.703703703703</v>
+        <v>10.714285714285</v>
       </c>
       <c r="M23" s="15">
-        <v>211.111111111111</v>
+        <v>244.444444444444</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-27.272727272727</v>
+        <v>15</v>
       </c>
       <c r="F24" s="14">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G24" s="14">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.528925619834</v>
+        <v>-9.909909909909</v>
       </c>
       <c r="I24" s="14">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="J24" s="14">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="K24" s="15">
-        <v>-29.711751662971</v>
+        <v>-27.600849256900</v>
       </c>
       <c r="L24" s="15">
-        <v>3.257328990228</v>
+        <v>-6.318681318681</v>
       </c>
       <c r="M24" s="15">
-        <v>31.535269709543</v>
+        <v>31.153846153846</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>18</v>
+      </c>
+      <c r="D25" s="14">
         <v>13</v>
       </c>
-      <c r="D25" s="14">
-        <v>24</v>
-      </c>
       <c r="E25" s="15">
-        <v>-45.833333333333</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F25" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G25" s="14">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H25" s="15">
-        <v>-19.480519480519</v>
+        <v>-9.859154929577</v>
       </c>
       <c r="I25" s="14">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="J25" s="14">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="K25" s="15">
-        <v>-40.390879478827</v>
+        <v>-36.875</v>
       </c>
       <c r="L25" s="15">
-        <v>-3.684210526315</v>
+        <v>-14.767932489451</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-12.5</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H26" s="15">
-        <v>-40</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="I26" s="14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J26" s="14">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K26" s="15">
-        <v>-17.355371900826</v>
+        <v>-12.698412698412</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.912621359223</v>
+        <v>0.917431192660</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.032786885245</v>
+        <v>-16.030534351145</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L27" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
+        <v>2</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>-30</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L28" s="15">
         <v>-46.153846153846</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L29" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.103448275862</v>
+        <v>-89.655172413793</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="M30" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="N30" s="15">
-        <v>-92</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,35 +854,35 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>2</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>2</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-50</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>0</v>
       </c>
       <c r="N14" s="15">
         <v>-83.333333333333</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
@@ -899,34 +899,34 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-25</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J16" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K16" s="15">
-        <v>-13.513513513513</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L16" s="15">
-        <v>-47.540983606557</v>
+        <v>-46.031746031746</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.540983606557</v>
+        <v>-46.875</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.610878661087</v>
+        <v>-86.561264822134</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>37.5</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>-12</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I17" s="14">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J17" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K17" s="15">
-        <v>15.714285714285</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L17" s="15">
-        <v>1.25</v>
+        <v>1.204819277108</v>
       </c>
       <c r="M17" s="15">
-        <v>37.288135593220</v>
+        <v>40</v>
       </c>
       <c r="N17" s="15">
-        <v>-53.977272727272</v>
+        <v>-54.838709677419</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>20</v>
+        <v>233.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
         <v>25</v>
       </c>
       <c r="K18" s="15">
-        <v>-4</v>
+        <v>16</v>
       </c>
       <c r="L18" s="15">
-        <v>-20</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="M18" s="15">
-        <v>-27.272727272727</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.697674418604</v>
+        <v>-89.377289377289</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-28.571428571428</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>-38.709677419354</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="J19" s="14">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K19" s="15">
-        <v>7.865168539325</v>
+        <v>4.081632653061</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.423841059602</v>
+        <v>-37.423312883435</v>
       </c>
       <c r="M19" s="15">
-        <v>11.627906976744</v>
+        <v>12.087912087912</v>
       </c>
       <c r="N19" s="15">
-        <v>-26.717557251908</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,11 +1100,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F20" s="14">
         <v>1</v>
@@ -1125,13 +1125,13 @@
         <v>-20</v>
       </c>
       <c r="L20" s="15">
-        <v>-42.857142857142</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.313725490196</v>
+        <v>-84.905660377358</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G21" s="17">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.428571428571</v>
+        <v>-17.567567567567</v>
       </c>
       <c r="I21" s="17">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="J21" s="17">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="K21" s="18">
-        <v>5.508474576271</v>
+        <v>2.702702702702</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.979472140762</v>
+        <v>-26.519337016574</v>
       </c>
       <c r="M21" s="18">
-        <v>1.632653061224</v>
+        <v>1.915708812260</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.542857142857</v>
+        <v>-71.180931744312</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,31 +1180,31 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>13</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>160</v>
+        <v>116.666666666667</v>
       </c>
       <c r="L22" s="15">
         <v>85.714285714285</v>
@@ -1213,48 +1213,48 @@
         <v>116.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>3</v>
-      </c>
-      <c r="D23" s="13" t="s">
+      <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>166.666666666667</v>
+        <v>75</v>
       </c>
       <c r="I23" s="14">
         <v>31</v>
       </c>
       <c r="J23" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K23" s="15">
-        <v>40.909090909090</v>
+        <v>34.782608695652</v>
       </c>
       <c r="L23" s="15">
-        <v>10.714285714285</v>
+        <v>3.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>244.444444444444</v>
+        <v>210</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>15</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F24" s="14">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G24" s="14">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.909909909909</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="I24" s="14">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="J24" s="14">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="K24" s="15">
-        <v>-27.600849256900</v>
+        <v>-25.557809330628</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.318681318681</v>
+        <v>-6.377551020408</v>
       </c>
       <c r="M24" s="15">
-        <v>31.153846153846</v>
+        <v>30.141843971631</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>38.461538461538</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F25" s="14">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G25" s="14">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H25" s="15">
-        <v>-9.859154929577</v>
+        <v>-15.068493150684</v>
       </c>
       <c r="I25" s="14">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="J25" s="14">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="K25" s="15">
-        <v>-36.875</v>
+        <v>-35.905044510385</v>
       </c>
       <c r="L25" s="15">
-        <v>-14.767932489451</v>
+        <v>-14.624505928853</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
         <v>37</v>
       </c>
       <c r="H26" s="15">
-        <v>-18.918918918918</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="I26" s="14">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="J26" s="14">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.698412698412</v>
+        <v>-13.868613138686</v>
       </c>
       <c r="L26" s="15">
-        <v>0.917431192660</v>
+        <v>-0.840336134453</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.030534351145</v>
+        <v>-19.727891156462</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1387,38 +1387,38 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L27" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1438,66 +1438,66 @@
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
         <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>-41.666666666666</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L28" s="15">
-        <v>-46.153846153846</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="13" t="s">
+      <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>2</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N29" s="15">
         <v>-89.655172413793</v>
@@ -1507,38 +1507,38 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>100</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L30" s="15">
         <v>-40</v>
       </c>
       <c r="M30" s="15">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N30" s="15">
         <v>-88</v>
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1576,13 +1576,13 @@
         <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="15">
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>71</v>

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>2</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
         <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -890,25 +890,25 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="14">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
@@ -920,7 +920,7 @@
         <v>75</v>
       </c>
       <c r="L15" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="M15" s="15">
         <v>133.333333333333</v>
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
         <v>5</v>
       </c>
-      <c r="E16" s="15">
-        <v>-60</v>
-      </c>
-      <c r="F16" s="14">
-        <v>6</v>
-      </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K16" s="15">
-        <v>-19.047619047619</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L16" s="15">
-        <v>-46.031746031746</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M16" s="15">
-        <v>-46.875</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.561264822134</v>
+        <v>-86.259541984732</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" s="15">
-        <v>-22.222222222222</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="I17" s="14">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J17" s="14">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K17" s="15">
-        <v>9.090909090909</v>
+        <v>2.352941176470</v>
       </c>
       <c r="L17" s="15">
-        <v>1.204819277108</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>40</v>
+        <v>40.322580645161</v>
       </c>
       <c r="N17" s="15">
-        <v>-54.838709677419</v>
+        <v>-56.281407035175</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
         <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>233.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J18" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>16</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.121212121212</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M18" s="15">
-        <v>-17.142857142857</v>
+        <v>-25</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.377289377289</v>
+        <v>-89.966555183946</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.222222222222</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G19" s="14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>-33.333333333333</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I19" s="14">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="J19" s="14">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K19" s="15">
-        <v>4.081632653061</v>
+        <v>8.910891089108</v>
       </c>
       <c r="L19" s="15">
-        <v>-37.423312883435</v>
+        <v>-36.781609195402</v>
       </c>
       <c r="M19" s="15">
-        <v>12.087912087912</v>
+        <v>15.789473684210</v>
       </c>
       <c r="N19" s="15">
-        <v>-25</v>
+        <v>-21.428571428571</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1104,16 +1104,16 @@
         <v>20</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>1</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
@@ -1131,7 +1131,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.905660377358</v>
+        <v>-85.454545454545</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.739130434782</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>-17.567567567567</v>
+        <v>-13.235294117647</v>
       </c>
       <c r="I21" s="17">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="J21" s="17">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="K21" s="18">
-        <v>2.702702702702</v>
+        <v>2.564102564102</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.519337016574</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M21" s="18">
-        <v>1.915708812260</v>
+        <v>1.083032490974</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.180931744312</v>
+        <v>-71.340839303991</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,79 +1182,79 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="14">
         <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>116.666666666667</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>85.714285714285</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>116.666666666667</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J23" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K23" s="15">
-        <v>34.782608695652</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>3.333333333333</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="M23" s="15">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>18.181818181818</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="F24" s="14">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G24" s="14">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H24" s="15">
-        <v>-2.941176470588</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="J24" s="14">
-        <v>493</v>
+        <v>526</v>
       </c>
       <c r="K24" s="15">
-        <v>-25.557809330628</v>
+        <v>-26.996197718631</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.377551020408</v>
+        <v>-9.433962264150</v>
       </c>
       <c r="M24" s="15">
-        <v>30.141843971631</v>
+        <v>25.901639344262</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E25" s="15">
-        <v>-11.764705882352</v>
+        <v>-62.068965517241</v>
       </c>
       <c r="F25" s="14">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G25" s="14">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.068493150684</v>
+        <v>-32.530120481927</v>
       </c>
       <c r="I25" s="14">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="J25" s="14">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.905044510385</v>
+        <v>-37.978142076502</v>
       </c>
       <c r="L25" s="15">
-        <v>-14.624505928853</v>
+        <v>-17.454545454545</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,54 +1344,54 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>-27.272727272727</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>-21.621621621621</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I26" s="14">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J26" s="14">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.868613138686</v>
+        <v>-18.543046357615</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.840336134453</v>
+        <v>-0.806451612903</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.727891156462</v>
+        <v>-25</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1406,19 +1406,19 @@
         <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1438,28 +1438,28 @@
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>-46.153846153846</v>
+        <v>-56.25</v>
       </c>
       <c r="L28" s="15">
-        <v>-50</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
@@ -1497,10 +1497,10 @@
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.655172413793</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="14">
-        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1538,10 +1538,10 @@
         <v>-40</v>
       </c>
       <c r="M30" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-88</v>
+        <v>-89.655172413793</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1576,13 +1576,13 @@
         <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="15">
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>71</v>

--- a/data/source/weekly/cs-en-us-028pct.xlsx
+++ b/data/source/weekly/cs-en-us-028pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -920,13 +920,13 @@
         <v>75</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M15" s="15">
         <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-30</v>
+        <v>-41.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.181818181818</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.454545454545</v>
+        <v>-44.117647058823</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.826086956521</v>
+        <v>-46.478873239436</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.259541984732</v>
+        <v>-86.281588447653</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-62.5</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>-26.923076923076</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17" s="14">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K17" s="15">
-        <v>2.352941176470</v>
+        <v>-1.123595505617</v>
       </c>
       <c r="L17" s="15">
-        <v>-3.333333333333</v>
+        <v>-7.368421052631</v>
       </c>
       <c r="M17" s="15">
-        <v>40.322580645161</v>
+        <v>31.343283582089</v>
       </c>
       <c r="N17" s="15">
-        <v>-56.281407035175</v>
+        <v>-59.817351598173</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>166.666666666667</v>
+        <v>350</v>
       </c>
       <c r="I18" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J18" s="14">
         <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>15.384615384615</v>
+        <v>19.230769230769</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.764705882352</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="M18" s="15">
-        <v>-25</v>
+        <v>-29.545454545454</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.966555183946</v>
+        <v>-90.095846645367</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>166.666666666667</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.692307692307</v>
+        <v>20</v>
       </c>
       <c r="I19" s="14">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J19" s="14">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K19" s="15">
-        <v>8.910891089108</v>
+        <v>12.149532710280</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.781609195402</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="M19" s="15">
-        <v>15.789473684210</v>
+        <v>21.212121212121</v>
       </c>
       <c r="N19" s="15">
-        <v>-21.428571428571</v>
+        <v>-16.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="14">
+      <c r="D20" s="14">
         <v>1</v>
       </c>
+      <c r="E20" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K20" s="15">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L20" s="15">
-        <v>-46.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M20" s="15">
         <v>33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.454545454545</v>
+        <v>-85.964912280701</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,45 +1142,45 @@
         <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.235294117647</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="I21" s="17">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="J21" s="17">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="K21" s="18">
-        <v>2.564102564102</v>
+        <v>3.157894736842</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.272727272727</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="M21" s="18">
-        <v>1.083032490974</v>
+        <v>0.684931506849</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.340839303991</v>
+        <v>-71.566731141199</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>133.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
         <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J23" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K23" s="15">
-        <v>33.333333333333</v>
+        <v>36</v>
       </c>
       <c r="L23" s="15">
-        <v>-3.030303030303</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M23" s="15">
-        <v>220</v>
+        <v>209.090909090909</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>-48.484848484848</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="F24" s="14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G24" s="14">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.666666666666</v>
+        <v>-12.844036697247</v>
       </c>
       <c r="I24" s="14">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="J24" s="14">
-        <v>526</v>
+        <v>560</v>
       </c>
       <c r="K24" s="15">
-        <v>-26.996197718631</v>
+        <v>-26.25</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.433962264150</v>
+        <v>-8.425720620842</v>
       </c>
       <c r="M24" s="15">
-        <v>25.901639344262</v>
+        <v>24.397590361445</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E25" s="15">
-        <v>-62.068965517241</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="F25" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G25" s="14">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.530120481927</v>
+        <v>-27.058823529411</v>
       </c>
       <c r="I25" s="14">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="J25" s="14">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="K25" s="15">
-        <v>-37.978142076502</v>
+        <v>-37.244897959183</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.454545454545</v>
+        <v>-13.684210526315</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-71.428571428571</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>-21.052631578947</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I26" s="14">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="J26" s="14">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="K26" s="15">
-        <v>-18.543046357615</v>
+        <v>-18.404907975460</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.806451612903</v>
+        <v>0.757575757575</v>
       </c>
       <c r="M26" s="15">
-        <v>-25</v>
+        <v>-22.674418604651</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1412,7 +1412,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
@@ -1444,16 +1444,16 @@
         <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
         <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>-56.25</v>
+        <v>-43.75</v>
       </c>
       <c r="L28" s="15">
-        <v>-53.333333333333</v>
+        <v>-43.75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-62.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-62.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-89.655172413793</v>
+        <v>-90.322580645161</v>
       </c>
     </row>
     <row r="31" spans="1:14">
